--- a/xlsx/Power/p10.xlsx
+++ b/xlsx/Power/p10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CEAD12-A3B3-482B-9236-4FE22E5686C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609CFE9D-DDA6-4556-A46A-A17774ABE686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{CAC09CFB-6F35-434A-A405-32B77C398EFF}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{CAC09CFB-6F35-434A-A405-32B77C398EFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,16 +404,16 @@
         <v>0.85199999999999998</v>
       </c>
       <c r="C1">
-        <v>0.97199999999999998</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="D1">
-        <v>0.997</v>
+        <v>0.91700000000000004</v>
       </c>
       <c r="E1">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="F1">
         <v>0.999</v>
-      </c>
-      <c r="F1">
-        <v>1</v>
       </c>
       <c r="G1">
         <v>1</v>
@@ -436,16 +436,16 @@
         <v>0.79100000000000004</v>
       </c>
       <c r="C2">
-        <v>0.94799999999999995</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="D2">
-        <v>0.99099999999999999</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="E2">
-        <v>0.998</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0.997</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -468,7 +468,7 @@
         <v>0.78</v>
       </c>
       <c r="C3">
-        <v>0.94</v>
+        <v>0.95799999999999996</v>
       </c>
       <c r="D3">
         <v>0.98599999999999999</v>
@@ -494,13 +494,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.39700000000000002</v>
+        <v>0.42599999999999999</v>
       </c>
       <c r="B4">
-        <v>0.72799999999999998</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="C4">
-        <v>0.88900000000000001</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="D4">
         <v>0.97099999999999997</v>
@@ -564,16 +564,16 @@
         <v>0.63300000000000001</v>
       </c>
       <c r="C6">
-        <v>0.81200000000000006</v>
+        <v>0.96099999999999997</v>
       </c>
       <c r="D6">
-        <v>0.93500000000000005</v>
+        <v>0.96299999999999997</v>
       </c>
       <c r="E6">
-        <v>0.96599999999999997</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="F6">
-        <v>0.99099999999999999</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -596,16 +596,16 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="C7">
-        <v>0.75700000000000001</v>
+        <v>0.749</v>
       </c>
       <c r="D7">
-        <v>0.88900000000000001</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="E7">
-        <v>0.94399999999999995</v>
+        <v>0.94599999999999995</v>
       </c>
       <c r="F7">
-        <v>0.98599999999999999</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="G7">
         <v>0.996</v>
@@ -628,19 +628,19 @@
         <v>0.81799999999999995</v>
       </c>
       <c r="C8">
-        <v>0.94699999999999995</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="D8">
-        <v>0.99</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="E8">
-        <v>0.998</v>
+        <v>0.97399999999999998</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -660,28 +660,28 @@
         <v>0.45</v>
       </c>
       <c r="C9">
-        <v>0.27700000000000002</v>
+        <v>0.73</v>
       </c>
       <c r="D9">
-        <v>0.185</v>
+        <v>0.98</v>
       </c>
       <c r="E9">
-        <v>0.191</v>
+        <v>0.871</v>
       </c>
       <c r="F9">
-        <v>0.26</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="G9">
-        <v>0.32</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="H9">
-        <v>0.371</v>
+        <v>0.435</v>
       </c>
       <c r="I9">
-        <v>0.47399999999999998</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="J9">
-        <v>0.52600000000000002</v>
+        <v>0.55200000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p10.xlsx
+++ b/xlsx/Power/p10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609CFE9D-DDA6-4556-A46A-A17774ABE686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75AB0A0-021E-4C07-B1DD-159794CEE369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{CAC09CFB-6F35-434A-A405-32B77C398EFF}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{CAC09CFB-6F35-434A-A405-32B77C398EFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -401,19 +401,19 @@
         <v>0.45600000000000002</v>
       </c>
       <c r="B1">
-        <v>0.85199999999999998</v>
+        <v>0.85299999999999998</v>
       </c>
       <c r="C1">
-        <v>0.53600000000000003</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="D1">
-        <v>0.91700000000000004</v>
+        <v>0.997</v>
       </c>
       <c r="E1">
-        <v>0.98499999999999999</v>
+        <v>0.999</v>
       </c>
       <c r="F1">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="G1">
         <v>1</v>
@@ -436,16 +436,16 @@
         <v>0.79100000000000004</v>
       </c>
       <c r="C2">
-        <v>0.52600000000000002</v>
+        <v>0.94799999999999995</v>
       </c>
       <c r="D2">
-        <v>0.88900000000000001</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="E2">
-        <v>0.97499999999999998</v>
+        <v>0.998</v>
       </c>
       <c r="F2">
-        <v>0.997</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -468,7 +468,7 @@
         <v>0.78</v>
       </c>
       <c r="C3">
-        <v>0.95799999999999996</v>
+        <v>0.94</v>
       </c>
       <c r="D3">
         <v>0.98599999999999999</v>
@@ -494,13 +494,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.42599999999999999</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="B4">
-        <v>0.74099999999999999</v>
+        <v>0.72799999999999998</v>
       </c>
       <c r="C4">
-        <v>0.89300000000000002</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="D4">
         <v>0.97099999999999997</v>
@@ -564,16 +564,16 @@
         <v>0.63300000000000001</v>
       </c>
       <c r="C6">
-        <v>0.96099999999999997</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="D6">
-        <v>0.96299999999999997</v>
+        <v>0.93500000000000005</v>
       </c>
       <c r="E6">
-        <v>0.97499999999999998</v>
+        <v>0.96599999999999997</v>
       </c>
       <c r="F6">
-        <v>0.99399999999999999</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -596,16 +596,16 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="C7">
-        <v>0.749</v>
+        <v>0.75700000000000001</v>
       </c>
       <c r="D7">
-        <v>0.88600000000000001</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="E7">
-        <v>0.94599999999999995</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="F7">
-        <v>0.98499999999999999</v>
+        <v>0.98599999999999999</v>
       </c>
       <c r="G7">
         <v>0.996</v>
@@ -625,22 +625,22 @@
         <v>0.315</v>
       </c>
       <c r="B8">
-        <v>0.81799999999999995</v>
+        <v>0.81699999999999995</v>
       </c>
       <c r="C8">
-        <v>6.0999999999999999E-2</v>
+        <v>0.94699999999999995</v>
       </c>
       <c r="D8">
-        <v>0.85599999999999998</v>
+        <v>0.99</v>
       </c>
       <c r="E8">
-        <v>0.97399999999999998</v>
+        <v>0.998</v>
       </c>
       <c r="F8">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -660,28 +660,28 @@
         <v>0.45</v>
       </c>
       <c r="C9">
-        <v>0.73</v>
+        <v>0.27700000000000002</v>
       </c>
       <c r="D9">
-        <v>0.98</v>
+        <v>0.185</v>
       </c>
       <c r="E9">
-        <v>0.871</v>
+        <v>0.191</v>
       </c>
       <c r="F9">
-        <v>0.45700000000000002</v>
+        <v>0.26</v>
       </c>
       <c r="G9">
-        <v>0.44900000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="H9">
-        <v>0.435</v>
+        <v>0.371</v>
       </c>
       <c r="I9">
-        <v>0.52100000000000002</v>
+        <v>0.47399999999999998</v>
       </c>
       <c r="J9">
-        <v>0.55200000000000005</v>
+        <v>0.52600000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p10.xlsx
+++ b/xlsx/Power/p10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75AB0A0-021E-4C07-B1DD-159794CEE369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64DFE379-C6E9-4ECC-BD54-3335606119D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{CAC09CFB-6F35-434A-A405-32B77C398EFF}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{CAC09CFB-6F35-434A-A405-32B77C398EFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,10 +398,10 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.45600000000000002</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="B1">
-        <v>0.85299999999999998</v>
+        <v>0.85399999999999998</v>
       </c>
       <c r="C1">
         <v>0.97199999999999998</v>
@@ -430,13 +430,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.42899999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="B2">
-        <v>0.79100000000000004</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="C2">
-        <v>0.94799999999999995</v>
+        <v>0.95</v>
       </c>
       <c r="D2">
         <v>0.99099999999999999</v>
@@ -462,13 +462,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.42499999999999999</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="B3">
-        <v>0.78</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="C3">
-        <v>0.94</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="D3">
         <v>0.98599999999999999</v>
@@ -494,16 +494,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.39700000000000002</v>
+        <v>0.39400000000000002</v>
       </c>
       <c r="B4">
-        <v>0.72799999999999998</v>
+        <v>0.73</v>
       </c>
       <c r="C4">
-        <v>0.88900000000000001</v>
+        <v>0.89300000000000002</v>
       </c>
       <c r="D4">
-        <v>0.97099999999999997</v>
+        <v>0.97199999999999998</v>
       </c>
       <c r="E4">
         <v>0.99099999999999999</v>
@@ -526,48 +526,48 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.79800000000000004</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.879</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.92500000000000004</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.33800000000000002</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="B6">
         <v>0.63300000000000001</v>
       </c>
       <c r="C6">
-        <v>0.81200000000000006</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="D6">
-        <v>0.93500000000000005</v>
+        <v>0.93400000000000005</v>
       </c>
       <c r="E6">
         <v>0.96599999999999997</v>
@@ -590,22 +590,22 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.309</v>
+        <v>0.30199999999999999</v>
       </c>
       <c r="B7">
-        <v>0.56999999999999995</v>
+        <v>0.56899999999999995</v>
       </c>
       <c r="C7">
-        <v>0.75700000000000001</v>
+        <v>0.754</v>
       </c>
       <c r="D7">
-        <v>0.88900000000000001</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="E7">
         <v>0.94399999999999995</v>
       </c>
       <c r="F7">
-        <v>0.98599999999999999</v>
+        <v>0.98499999999999999</v>
       </c>
       <c r="G7">
         <v>0.996</v>
@@ -625,7 +625,7 @@
         <v>0.315</v>
       </c>
       <c r="B8">
-        <v>0.81699999999999995</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="C8">
         <v>0.94699999999999995</v>
@@ -654,34 +654,34 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>0.224</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="B9">
-        <v>0.45</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="C9">
         <v>0.27700000000000002</v>
       </c>
       <c r="D9">
-        <v>0.185</v>
+        <v>0.188</v>
       </c>
       <c r="E9">
-        <v>0.191</v>
+        <v>0.188</v>
       </c>
       <c r="F9">
-        <v>0.26</v>
+        <v>0.26100000000000001</v>
       </c>
       <c r="G9">
-        <v>0.32</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="H9">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="I9">
-        <v>0.47399999999999998</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="J9">
-        <v>0.52600000000000002</v>
+        <v>0.53200000000000003</v>
       </c>
     </row>
   </sheetData>
